--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.48761275116071</v>
+        <v>2.679237072063616</v>
       </c>
       <c r="D2" t="n">
-        <v>17.5202194909516</v>
+        <v>2.847035667279635</v>
       </c>
       <c r="E2" t="n">
-        <v>18.2668522356064</v>
+        <v>2.96836348828604</v>
       </c>
       <c r="F2" t="n">
-        <v>18.16136039060486</v>
+        <v>2.95122106347329</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.73555950697329</v>
+        <v>10.51952841988316</v>
       </c>
       <c r="D3" t="n">
-        <v>65.42962173125224</v>
+        <v>10.63231353132849</v>
       </c>
       <c r="E3" t="n">
-        <v>18.2668522356064</v>
+        <v>2.96836348828604</v>
       </c>
       <c r="F3" t="n">
-        <v>18.16136039060486</v>
+        <v>2.95122106347329</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.62309243979326</v>
+        <v>3.676252521466405</v>
       </c>
       <c r="D4" t="n">
-        <v>30.67755448166128</v>
+        <v>4.985102603269957</v>
       </c>
       <c r="E4" t="n">
-        <v>18.2668522356064</v>
+        <v>2.96836348828604</v>
       </c>
       <c r="F4" t="n">
-        <v>18.16136039060486</v>
+        <v>2.95122106347329</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.95251913402125</v>
+        <v>2.754784359278453</v>
       </c>
       <c r="D5" t="n">
-        <v>16.9192261366968</v>
+        <v>2.74937424721323</v>
       </c>
       <c r="E5" t="n">
-        <v>18.2668522356064</v>
+        <v>2.96836348828604</v>
       </c>
       <c r="F5" t="n">
-        <v>18.16136039060486</v>
+        <v>2.95122106347329</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.92701944393314</v>
+        <v>3.563140659639136</v>
       </c>
       <c r="D6" t="n">
-        <v>21.77306249228626</v>
+        <v>3.538122654996517</v>
       </c>
       <c r="E6" t="n">
-        <v>18.2668522356064</v>
+        <v>2.96836348828604</v>
       </c>
       <c r="F6" t="n">
-        <v>18.16136039060486</v>
+        <v>2.95122106347329</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
